--- a/samples/02_회사양식_변환/회사양식_SO입력_PO-ACME-2026-0417.xlsx
+++ b/samples/02_회사양식_변환/회사양식_SO입력_PO-ACME-2026-0417.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_Upload" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="열설명" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SO_Upload" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="열설명" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -156,9 +156,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SO_Upload" displayName="SO_Upload" ref="A1:S5" headerRowCount="1">
-  <autoFilter ref="A1:S5"/>
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SO_Upload" displayName="SO_Upload" ref="A1:V5" headerRowCount="1">
+  <autoFilter ref="A1:V5"/>
+  <tableColumns count="22">
     <tableColumn id="1" name="Order Date"/>
     <tableColumn id="2" name="Customer Code"/>
     <tableColumn id="3" name="Customer Name"/>
@@ -178,6 +178,9 @@
     <tableColumn id="17" name="Customer Contact"/>
     <tableColumn id="18" name="Entered By"/>
     <tableColumn id="19" name="Remarks"/>
+    <tableColumn id="20" name="HQ Unit Price"/>
+    <tableColumn id="21" name="HQ Amount"/>
+    <tableColumn id="22" name="Markup %"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -472,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -494,6 +497,9 @@
     <col width="27" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,6 +598,21 @@
           <t>Remarks</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HQ Unit Price</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HQ Amount</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Markup %</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -673,6 +694,15 @@
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="4" t="n">
+        <v>49955</v>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>99910</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -754,6 +784,15 @@
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="4" t="n">
+        <v>1887</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>7548</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -835,6 +874,15 @@
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="4" t="n">
+        <v>267.8</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>6427.2</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -916,6 +964,15 @@
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>950</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -931,11 +988,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1070,6 +1127,30 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HQ Unit Price / HQ Amount</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>본사 단가 = Unit Price x (1 + Markup % / 100), HQ Amount = Qty x 본사 단가 (마크업표)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Markup %</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>마크업표의 그 파트 마크업% (3 = 3%)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
